--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1.898596650151424</v>
+        <v>0.3085219556496065</v>
       </c>
       <c r="D2" t="n">
-        <v>2.54382881295726</v>
+        <v>0.4133721821055548</v>
       </c>
       <c r="E2" t="n">
-        <v>29.25290271764448</v>
+        <v>4.753596691617227</v>
       </c>
       <c r="F2" t="n">
-        <v>26.26666140942803</v>
+        <v>4.268332479032057</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.466025672829909</v>
+        <v>0.7257291718348603</v>
       </c>
       <c r="D3" t="n">
-        <v>5.081825621774808</v>
+        <v>0.8257966635384063</v>
       </c>
       <c r="E3" t="n">
-        <v>29.25290271764448</v>
+        <v>4.753596691617227</v>
       </c>
       <c r="F3" t="n">
-        <v>26.26666140942803</v>
+        <v>4.268332479032057</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.399912349688938</v>
+        <v>1.527485756824452</v>
       </c>
       <c r="D4" t="n">
-        <v>4.164180482880044</v>
+        <v>0.6766793284680073</v>
       </c>
       <c r="E4" t="n">
-        <v>29.25290271764448</v>
+        <v>4.753596691617227</v>
       </c>
       <c r="F4" t="n">
-        <v>26.26666140942803</v>
+        <v>4.268332479032057</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>72.52406566217252</v>
+        <v>11.78516067010303</v>
       </c>
       <c r="D5" t="n">
-        <v>64.55388956077084</v>
+        <v>10.49000705362526</v>
       </c>
       <c r="E5" t="n">
-        <v>29.25290271764448</v>
+        <v>4.753596691617227</v>
       </c>
       <c r="F5" t="n">
-        <v>26.26666140942803</v>
+        <v>4.268332479032057</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
